--- a/Practise_Excel.xlsx
+++ b/Practise_Excel.xlsx
@@ -8,23 +8,55 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91880\Desktop\STUDY MATERIAL DS\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9A1D92-435C-4B68-8D41-7E37C6F7F4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAEBE43-66AE-4E79-89E3-0E3AEDC4B127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Q3" sheetId="4" r:id="rId2"/>
-    <sheet name="Q2" sheetId="3" r:id="rId3"/>
-    <sheet name="Q1" sheetId="2" r:id="rId4"/>
+    <sheet name="Q7" sheetId="8" r:id="rId2"/>
+    <sheet name="Q6" sheetId="7" r:id="rId3"/>
+    <sheet name="Q3" sheetId="4" r:id="rId4"/>
+    <sheet name="Q2" sheetId="3" r:id="rId5"/>
+    <sheet name="Q1" sheetId="2" r:id="rId6"/>
+    <sheet name="Q4" sheetId="5" r:id="rId7"/>
+    <sheet name="Q5" sheetId="6" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$C$11:$G$11</definedName>
+    <definedName name="_xlcn.WorksheetConnection_Practise_Excel.xlsxData1" hidden="1">Data[]</definedName>
+    <definedName name="Slicer_Sales_Person">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="146" r:id="rId9"/>
+    <pivotCache cacheId="147" r:id="rId10"/>
+    <pivotCache cacheId="196" r:id="rId11"/>
+    <pivotCache cacheId="213" r:id="rId12"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
+      <x14:pivotCaches>
+        <pivotCache cacheId="59" r:id="rId13"/>
+      </x14:pivotCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId14"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
+      <x15:dataModel>
+        <x15:modelTables>
+          <x15:modelTable id="Data" name="Data" connection="WorksheetConnection_Practise_Excel.xlsx!Data"/>
+        </x15:modelTables>
+      </x15:dataModel>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,8 +71,31 @@
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{A41FCB68-C6A2-4F38-A2FF-116888DADC58}" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="8" minRefreshableVersion="5" background="1">
+    <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
+    <olapPr sendLocale="1" rowDrillCount="1000"/>
+    <extLst>
+      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
+        <x15:connection id="" model="1"/>
+      </ext>
+    </extLst>
+  </connection>
+  <connection id="2" xr16:uid="{A65F7449-47A8-43C7-A114-D27ECD0A5595}" name="WorksheetConnection_Practise_Excel.xlsx!Data" type="102" refreshedVersion="8" minRefreshableVersion="5">
+    <extLst>
+      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
+        <x15:connection id="Data" autoDelete="1">
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Practise_Excel.xlsxData1"/>
+        </x15:connection>
+      </ext>
+    </extLst>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1868" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="77">
   <si>
     <t>Product</t>
   </si>
@@ -245,22 +300,50 @@
   <si>
     <t>Country</t>
   </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Sum of Amount</t>
+  </si>
+  <si>
+    <t>Sum of Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                </t>
+  </si>
+  <si>
+    <t>What is pivot table?</t>
+  </si>
+  <si>
+    <t>Sales Per Unit</t>
+  </si>
+  <si>
+    <t>Top Sales By Country</t>
+  </si>
+  <si>
+    <t>Bottom Sales By Country</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="\$#,##0.0;\(\$#,##0.0\);\$#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,15 +411,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="0"/>
+      <sz val="18"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,6 +486,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -490,7 +606,7 @@
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -537,6 +653,25 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -570,9 +705,6 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -585,44 +717,45 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="38">
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -667,124 +800,82 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0.0_);_([$$-409]* \(#,##0.0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0.0_);_([$$-409]* \(#,##0.0\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
@@ -904,40 +995,1037 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>246467</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>172896</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>472965</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>173422</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Sales Person">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{625ABFDD-439F-61E1-C322-35EFA3D89AAD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Sales Person"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4077488" y="472441"/>
+              <a:ext cx="3274498" cy="1471974"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="RASIKA DESHMUKH" refreshedDate="46106.462141550925" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{C2C6852A-9B42-4C1E-8002-9C3E780FBA9C}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="5">
+    <cacheField name="[Measures].[Sum of Amount]" caption="Sum of Amount" numFmtId="0" hierarchy="8" level="32767"/>
+    <cacheField name="[Data].[Geography].[Geography]" caption="Geography" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems count="6">
+        <s v="Australia"/>
+        <s v="Canada"/>
+        <s v="India"/>
+        <s v="New Zealand"/>
+        <s v="UK"/>
+        <s v="USA"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Sum of Units]" caption="Sum of Units" numFmtId="0" hierarchy="9" level="32767"/>
+    <cacheField name="[Data].[Sales Person].[Sales Person]" caption="Sales Person" numFmtId="0" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="Unsupported0" numFmtId="0" hierarchy="11" level="32767">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{63CAB8AC-B538-458d-9737-405883B0398D}">
+          <x14:cacheField ignore="1"/>
+        </ext>
+      </extLst>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="12">
+    <cacheHierarchy uniqueName="[Data].[Sales Person]" caption="Sales Person" attribute="1" defaultMemberUniqueName="[Data].[Sales Person].[All]" allUniqueName="[Data].[Sales Person].[All]" dimensionUniqueName="[Data]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Data].[Geography]" caption="Geography" attribute="1" defaultMemberUniqueName="[Data].[Geography].[All]" allUniqueName="[Data].[Geography].[All]" dimensionUniqueName="[Data]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Data].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Data].[Product].[All]" allUniqueName="[Data].[Product].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Amount]" caption="Amount" attribute="1" defaultMemberUniqueName="[Data].[Amount].[All]" allUniqueName="[Data].[Amount].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Units]" caption="Units" attribute="1" defaultMemberUniqueName="[Data].[Units].[All]" allUniqueName="[Data].[Units].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Sales Per Unit]" caption="Sales Per Unit" measure="1" displayFolder="" measureGroup="Data" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Data]" caption="__XL_Count Data" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Amount]" caption="Sum of Amount" measure="1" displayFolder="" measureGroup="Data" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Units]" caption="Sum of Units" measure="1" displayFolder="" measureGroup="Data" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Geography]" caption="Count of Geography" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="Unsupported0" caption="Sales Person" measure="1" count="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{8CF416AD-EC4C-4aba-99F5-12A058AE0983}">
+          <x14:cacheHierarchy ignore="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension name="Data" uniqueName="[Data]" caption="Data"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Data" caption="Data"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="0"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="RASIKA DESHMUKH" refreshedDate="46106.482589930558" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{5CBE064E-08E1-4099-A226-87359FAE237D}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="2">
+    <cacheField name="[Data].[Product].[Product]" caption="Product" numFmtId="0" hierarchy="2" level="1">
+      <sharedItems count="5">
+        <s v="85% Dark Bars"/>
+        <s v="After Nines"/>
+        <s v="Baker's Choco Chips"/>
+        <s v="Peanut Butter Cubes"/>
+        <s v="Raspberry Choco"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Sales Per Unit]" caption="Sales Per Unit" numFmtId="0" hierarchy="5" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="11">
+    <cacheHierarchy uniqueName="[Data].[Sales Person]" caption="Sales Person" attribute="1" defaultMemberUniqueName="[Data].[Sales Person].[All]" allUniqueName="[Data].[Sales Person].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Geography]" caption="Geography" attribute="1" defaultMemberUniqueName="[Data].[Geography].[All]" allUniqueName="[Data].[Geography].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Data].[Product].[All]" allUniqueName="[Data].[Product].[All]" dimensionUniqueName="[Data]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Data].[Amount]" caption="Amount" attribute="1" defaultMemberUniqueName="[Data].[Amount].[All]" allUniqueName="[Data].[Amount].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Units]" caption="Units" attribute="1" defaultMemberUniqueName="[Data].[Units].[All]" allUniqueName="[Data].[Units].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Sales Per Unit]" caption="Sales Per Unit" measure="1" displayFolder="" measureGroup="Data" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Data]" caption="__XL_Count Data" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Amount]" caption="Sum of Amount" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Units]" caption="Sum of Units" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Geography]" caption="Count of Geography" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension name="Data" uniqueName="[Data]" caption="Data"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Data" caption="Data"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="0"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="RASIKA DESHMUKH" refreshedDate="46106.493435300923" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{4BDDDCB8-A4F4-49F4-8B2E-EB3F82E6C77B}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Data].[Sales Person].[Sales Person]" caption="Sales Person" numFmtId="0" level="1">
+      <sharedItems count="4">
+        <s v="Gigi Bohling"/>
+        <s v="Ches Bonnell"/>
+        <s v="Barr Faughny"/>
+        <s v="Ram Mahesh"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Sum of Amount]" caption="Sum of Amount" numFmtId="0" hierarchy="8" level="32767"/>
+    <cacheField name="[Data].[Geography].[Geography]" caption="Geography" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems count="6">
+        <s v="Australia"/>
+        <s v="Canada"/>
+        <s v="India"/>
+        <s v="New Zealand"/>
+        <s v="UK"/>
+        <s v="USA"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="11">
+    <cacheHierarchy uniqueName="[Data].[Sales Person]" caption="Sales Person" attribute="1" defaultMemberUniqueName="[Data].[Sales Person].[All]" allUniqueName="[Data].[Sales Person].[All]" dimensionUniqueName="[Data]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Data].[Geography]" caption="Geography" attribute="1" defaultMemberUniqueName="[Data].[Geography].[All]" allUniqueName="[Data].[Geography].[All]" dimensionUniqueName="[Data]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Data].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Data].[Product].[All]" allUniqueName="[Data].[Product].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Amount]" caption="Amount" attribute="1" defaultMemberUniqueName="[Data].[Amount].[All]" allUniqueName="[Data].[Amount].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Units]" caption="Units" attribute="1" defaultMemberUniqueName="[Data].[Units].[All]" allUniqueName="[Data].[Units].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Sales Per Unit]" caption="Sales Per Unit" measure="1" displayFolder="" measureGroup="Data" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Data]" caption="__XL_Count Data" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Amount]" caption="Sum of Amount" measure="1" displayFolder="" measureGroup="Data" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Units]" caption="Sum of Units" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Geography]" caption="Count of Geography" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension name="Data" uniqueName="[Data]" caption="Data"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Data" caption="Data"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="0"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="RASIKA DESHMUKH" refreshedDate="46106.493953935184" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{066FD129-7B49-4650-8A55-C60722A84F52}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Data].[Sales Person].[Sales Person]" caption="Sales Person" numFmtId="0" level="1">
+      <sharedItems count="4">
+        <s v="Carla Molina"/>
+        <s v="Brien Boise"/>
+        <s v="Oby Sorrel"/>
+        <s v="Barr Faughny"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Data].[Geography].[Geography]" caption="Geography" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems count="6">
+        <s v="Australia"/>
+        <s v="Canada"/>
+        <s v="India"/>
+        <s v="New Zealand"/>
+        <s v="UK"/>
+        <s v="USA"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Sum of Amount]" caption="Sum of Amount" numFmtId="0" hierarchy="8" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="11">
+    <cacheHierarchy uniqueName="[Data].[Sales Person]" caption="Sales Person" attribute="1" defaultMemberUniqueName="[Data].[Sales Person].[All]" allUniqueName="[Data].[Sales Person].[All]" dimensionUniqueName="[Data]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Data].[Geography]" caption="Geography" attribute="1" defaultMemberUniqueName="[Data].[Geography].[All]" allUniqueName="[Data].[Geography].[All]" dimensionUniqueName="[Data]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Data].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Data].[Product].[All]" allUniqueName="[Data].[Product].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Amount]" caption="Amount" attribute="1" defaultMemberUniqueName="[Data].[Amount].[All]" allUniqueName="[Data].[Amount].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Units]" caption="Units" attribute="1" defaultMemberUniqueName="[Data].[Units].[All]" allUniqueName="[Data].[Units].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Sales Per Unit]" caption="Sales Per Unit" measure="1" displayFolder="" measureGroup="Data" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Data]" caption="__XL_Count Data" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Amount]" caption="Sum of Amount" measure="1" displayFolder="" measureGroup="Data" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Units]" caption="Sum of Units" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of Geography]" caption="Count of Geography" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension name="Data" uniqueName="[Data]" caption="Data"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Data" caption="Data"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="0"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="RASIKA DESHMUKH" refreshedDate="46106.459143981483" backgroundQuery="1" createdVersion="3" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{E96EAFBA-0045-4D9E-899F-16D9F9916ABB}">
+  <cacheSource type="external" connectionId="1">
+    <extLst>
+      <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
+        <x14:sourceConnection name="ThisWorkbookDataModel"/>
+      </ext>
+    </extLst>
+  </cacheSource>
+  <cacheFields count="0"/>
+  <cacheHierarchies count="9">
+    <cacheHierarchy uniqueName="[Data].[Sales Person]" caption="Sales Person" attribute="1" defaultMemberUniqueName="[Data].[Sales Person].[All]" allUniqueName="[Data].[Sales Person].[All]" dimensionUniqueName="[Data]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Geography]" caption="Geography" attribute="1" defaultMemberUniqueName="[Data].[Geography].[All]" allUniqueName="[Data].[Geography].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Data].[Product].[All]" allUniqueName="[Data].[Product].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Amount]" caption="Amount" attribute="1" defaultMemberUniqueName="[Data].[Amount].[All]" allUniqueName="[Data].[Amount].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Data].[Units]" caption="Units" attribute="1" defaultMemberUniqueName="[Data].[Units].[All]" allUniqueName="[Data].[Units].[All]" dimensionUniqueName="[Data]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Data]" caption="__XL_Count Data" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Amount]" caption="Sum of Amount" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="3"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Units]" caption="Sum of Units" measure="1" displayFolder="" measureGroup="Data" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="4"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="1783578297" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C560704B-5426-4714-8FD5-0AA1F3E07680}" name="PivotTable6" cacheId="213" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="D5:E18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="11">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" id="1" iMeasureHier="8">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 top="0" val="1" filterVal="1"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <rowHierarchiesUsage count="2">
+    <rowHierarchyUsage hierarchyUsage="1"/>
+    <rowHierarchyUsage hierarchyUsage="0"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Practise_Excel.xlsx!Data">
+        <x15:activeTabTopLevelEntity name="[Data]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2711A51C-E66D-4C94-B4BB-746E71627248}" name="PivotTable4" cacheId="196" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A5:B18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="2"/>
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Amount" fld="1" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="11">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" id="1" iMeasureHier="8">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="1" filterVal="1"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <rowHierarchiesUsage count="2">
+    <rowHierarchyUsage hierarchyUsage="1"/>
+    <rowHierarchyUsage hierarchyUsage="0"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Practise_Excel.xlsx!Data">
+        <x15:activeTabTopLevelEntity name="[Data]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA57F732-33F4-4413-8381-5EE44C189A9F}" name="PivotTable2" cacheId="146" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:D9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" dragToRow="0" dragToCol="0" dragToPage="0" dragToData="0" dragOff="0" showAll="0" topAutoShow="0" includeNewItemsInFilter="1" itemPageCount="0" rankBy="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField ignore="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="Sum of Amount" fld="0" baseField="0" baseItem="0"/>
+    <dataField name="                                " fld="4" baseField="1" baseItem="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{E15A36E0-9728-4e99-A89B-3F7291B0FE68}">
+          <x14:dataField sourceField="0" uniqueName="[__Xl2].[Measures].[Sum of Amount]"/>
+        </ext>
+      </extLst>
+    </dataField>
+    <dataField name="Sum of Units" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="14">
+      <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <conditionalFormats count="1">
+    <conditionalFormat priority="1">
+      <pivotAreas count="1">
+        <pivotArea type="data" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="1"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotHierarchies count="12">
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1">
+      <members count="1" level="1">
+        <member name="[Data].[Sales Person].&amp;[Barr Faughny]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="                                "/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1" dragOff="0" includeNewItemsInFilter="1">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F1805F06-0CD3-4483-9156-8803C3D141DF}">
+          <x14:pivotHierarchy ignore="1"/>
+        </ext>
+      </extLst>
+    </pivotHierarchy>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="1"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Practise_Excel.xlsx!Data">
+        <x15:activeTabTopLevelEntity name="[Data]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{54665EC6-C106-47AF-A137-D732DFB1340C}" name="PivotTable3" cacheId="147" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="11">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" id="1" iMeasureHier="5">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="5" filterVal="5"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="2"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Practise_Excel.xlsx!Data">
+        <x15:activeTabTopLevelEntity name="[Data]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Sales_Person" xr10:uid="{7A9A5454-1062-4A10-8CF8-FF822203CB81}" sourceName="[Data].[Sales Person]">
+  <pivotTables>
+    <pivotTable tabId="5" name="PivotTable2"/>
+  </pivotTables>
+  <data>
+    <olap pivotCacheId="1783578297">
+      <levels count="2">
+        <level uniqueName="[Data].[Sales Person].[(All)]" sourceCaption="(All)" count="0"/>
+        <level uniqueName="[Data].[Sales Person].[Sales Person]" sourceCaption="Sales Person" count="10">
+          <ranges>
+            <range startItem="0">
+              <i n="[Data].[Sales Person].&amp;[Barr Faughny]" c="Barr Faughny"/>
+              <i n="[Data].[Sales Person].&amp;[Brien Boise]" c="Brien Boise"/>
+              <i n="[Data].[Sales Person].&amp;[Carla Molina]" c="Carla Molina"/>
+              <i n="[Data].[Sales Person].&amp;[Ches Bonnell]" c="Ches Bonnell"/>
+              <i n="[Data].[Sales Person].&amp;[Curtice Advani]" c="Curtice Advani"/>
+              <i n="[Data].[Sales Person].&amp;[Gigi Bohling]" c="Gigi Bohling"/>
+              <i n="[Data].[Sales Person].&amp;[Gunar Cockshoot]" c="Gunar Cockshoot"/>
+              <i n="[Data].[Sales Person].&amp;[Husein Augar]" c="Husein Augar"/>
+              <i n="[Data].[Sales Person].&amp;[Oby Sorrel]" c="Oby Sorrel"/>
+              <i n="[Data].[Sales Person].&amp;[Ram Mahesh]" c="Ram Mahesh"/>
+            </range>
+          </ranges>
+        </level>
+      </levels>
+      <selections count="1">
+        <selection n="[Data].[Sales Person].&amp;[Barr Faughny]"/>
+      </selections>
+    </olap>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Sales Person" xr10:uid="{3694784B-2280-415A-84C5-B34D494D3197}" cache="Slicer_Sales_Person" caption="Sales Person" columnCount="2" level="1" style="SlicerStyleDark1" rowHeight="234950"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="products" displayName="products" ref="Y11:Z33" totalsRowShown="0">
   <autoFilter ref="Y11:Z33" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Product"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Cost per unit" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Cost per unit" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{510FC75F-02FB-46E3-A2BC-BA9C886C030E}" name="Data" displayName="Data" ref="C11:G311" totalsRowShown="0" headerRowDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{510FC75F-02FB-46E3-A2BC-BA9C886C030E}" name="Data" displayName="Data" ref="C11:G311" totalsRowShown="0" headerRowDxfId="36">
   <autoFilter ref="C11:G311" xr:uid="{510FC75F-02FB-46E3-A2BC-BA9C886C030E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{4F3CAF24-2D7C-4F9E-AB6A-82D1D709787F}" name="Sales Person"/>
     <tableColumn id="2" xr3:uid="{4EA5CCBD-8412-4C1F-A179-369D28082C7B}" name="Geography"/>
     <tableColumn id="3" xr3:uid="{FCE85F75-80FF-4801-9998-9BDC2B74FDEE}" name="Product"/>
-    <tableColumn id="4" xr3:uid="{E11F4343-FCEE-4B50-98D6-AAD4973FBEC8}" name="Amount" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{D3F3BF20-04DD-466E-A23C-F464EE50485A}" name="Units" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{E11F4343-FCEE-4B50-98D6-AAD4973FBEC8}" name="Amount" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{D3F3BF20-04DD-466E-A23C-F464EE50485A}" name="Units" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{79ABE6F3-B1CC-49EB-88C5-3CDF6A1A7164}" name="Data4" displayName="Data4" ref="A3:E303" totalsRowShown="0" headerRowDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{79ABE6F3-B1CC-49EB-88C5-3CDF6A1A7164}" name="Data4" displayName="Data4" ref="A3:E303" totalsRowShown="0" headerRowDxfId="33">
   <autoFilter ref="A3:E303" xr:uid="{79ABE6F3-B1CC-49EB-88C5-3CDF6A1A7164}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{F3D9935D-7755-455F-9480-455D3CD05BDE}" name="Sales Person"/>
     <tableColumn id="2" xr3:uid="{22BDD93E-71E2-454D-B05E-BA9A44C9DC10}" name="Geography"/>
     <tableColumn id="3" xr3:uid="{343A653A-9DE0-4EBB-8AE7-41D636F6A989}" name="Product"/>
-    <tableColumn id="4" xr3:uid="{48ACA301-A67E-4168-8A75-1008F4475502}" name="Amount" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{8CA54C98-39E9-4FEB-8A3D-F08CF78D4835}" name="Units" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{48ACA301-A67E-4168-8A75-1008F4475502}" name="Amount" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{8CA54C98-39E9-4FEB-8A3D-F08CF78D4835}" name="Units" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7981,124 +9069,365 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A1F26F2-BFD9-4CDB-8CEC-70236091B923}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+    </row>
+    <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="D3" s="57" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="58"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="50"/>
+      <c r="D6" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="50"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="50">
+        <v>25221</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="50">
+        <v>6069</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="50"/>
+      <c r="D8" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="50"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="50">
+        <v>39620</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="50">
+        <v>5019</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="50"/>
+      <c r="D10" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="50"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="50">
+        <v>41559</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="50">
+        <v>5516</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="50"/>
+      <c r="D12" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="50"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="50">
+        <v>43568</v>
+      </c>
+      <c r="D13" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="50">
+        <v>7987</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="50"/>
+      <c r="D14" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="50"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="50">
+        <v>45752</v>
+      </c>
+      <c r="D15" s="53" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="50">
+        <v>3976</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="50"/>
+      <c r="D16" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="50"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="50">
+        <v>38325</v>
+      </c>
+      <c r="D17" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" s="50">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="50">
+        <v>234045</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" s="50">
+        <v>30709</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04F0A542-E831-49F5-97D1-6BAC727399B5}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF71245-1A3D-48A3-BC76-B16FEE863930}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.5546875" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="1.109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42" t="s">
+      <c r="C2" s="25"/>
+      <c r="D2" s="25" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="44">
+      <c r="B3" s="27">
         <f>SUMIFS(Data[Amount],Data[Geography],A3)</f>
         <v>218813</v>
       </c>
-      <c r="C3" s="45">
+      <c r="C3" s="28">
         <v>218813</v>
       </c>
-      <c r="D3" s="47">
+      <c r="D3" s="29">
         <v>7431</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="44">
+      <c r="B4" s="27">
         <f>SUMIFS(Data[Amount],Data[Geography],A4)</f>
         <v>189434</v>
       </c>
-      <c r="C4" s="45">
+      <c r="C4" s="28">
         <v>189434</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="29">
         <v>10158</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="44">
+      <c r="B5" s="27">
         <f>SUMIFS(Data[Amount],Data[Geography],A5)</f>
         <v>237944</v>
       </c>
-      <c r="C5" s="45">
+      <c r="C5" s="28">
         <v>237944</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="29">
         <v>7302</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="44">
+      <c r="B6" s="27">
         <f>SUMIFS(Data[Amount],Data[Geography],A6)</f>
         <v>173530</v>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="28">
         <v>173530</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="29">
         <v>5745</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="44">
+      <c r="B7" s="27">
         <f>SUMIFS(Data[Amount],Data[Geography],A7)</f>
         <v>168679</v>
       </c>
-      <c r="C7" s="45">
+      <c r="C7" s="28">
         <v>168679</v>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="29">
         <v>6264</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="44">
+      <c r="B8" s="27">
         <f>SUMIFS(Data[Amount],Data[Geography],A8)</f>
         <v>252469</v>
       </c>
-      <c r="C8" s="45">
+      <c r="C8" s="28">
         <v>252469</v>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="29">
         <v>8760</v>
       </c>
     </row>
@@ -8106,23 +9435,6 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D1">
-    <cfRule type="dataBar" priority="9">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7371C2E3-015B-4E85-AB48-12A7A3C703A1}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="10" operator="lessThan">
-      <formula>2000</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C2:C8">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="0">
@@ -8137,10 +9449,40 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D1">
+    <cfRule type="dataBar" priority="9">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{7371C2E3-015B-4E85-AB48-12A7A3C703A1}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="lessThan">
+      <formula>2000</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{BBD51D78-DF69-4FB4-80E7-ED5A5A8EBD58}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF0070C0"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C2:C8</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{7371C2E3-015B-4E85-AB48-12A7A3C703A1}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
@@ -8154,28 +9496,15 @@
           </x14:cfRule>
           <xm:sqref>D1</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{BBD51D78-DF69-4FB4-80E7-ED5A5A8EBD58}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FF0070C0"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>C2:C8</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6166E9FD-C1D1-44D7-8302-4020B1077F0A}">
-  <dimension ref="A1:H303"/>
+  <dimension ref="A1:E303"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -8188,19 +9517,16 @@
     <col min="8" max="8" width="9.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="A1" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>11</v>
       </c>
@@ -8217,7 +9543,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -8234,7 +9560,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -8251,7 +9577,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -8268,7 +9594,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -8285,7 +9611,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -8302,7 +9628,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -8319,7 +9645,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -8336,7 +9662,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -8353,7 +9679,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -8370,7 +9696,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -8387,7 +9713,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -8404,7 +9730,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -8421,7 +9747,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -13319,9 +14645,9 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3:D1048576 D1">
+  <conditionalFormatting sqref="D3:D1048576">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
@@ -13334,8 +14660,28 @@
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="lessThan">
       <formula>2000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:D303">
+    <cfRule type="top10" dxfId="2" priority="2" rank="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:E303">
+    <cfRule type="aboveAverage" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFB628"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{5619B905-08E7-4927-9397-FCD275D59FF8}</x14:id>
+        </ext>
+      </extLst>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6">
@@ -13351,26 +14697,6 @@
         </ext>
       </extLst>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFB628"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5619B905-08E7-4927-9397-FCD275D59FF8}</x14:id>
-        </ext>
-      </extLst>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D303">
-    <cfRule type="top10" dxfId="9" priority="2" rank="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E303">
-    <cfRule type="aboveAverage" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -13390,7 +14716,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D3:D1048576 D1</xm:sqref>
+          <xm:sqref>D3:D1048576</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{5619B905-08E7-4927-9397-FCD275D59FF8}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FFFFB628"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{690A1970-6F38-498D-BE78-9691CB89DBB1}">
@@ -13405,26 +14744,13 @@
           </x14:cfRule>
           <xm:sqref>I6</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{5619B905-08E7-4927-9397-FCD275D59FF8}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
-              <x14:cfvo type="autoMin"/>
-              <x14:cfvo type="autoMax"/>
-              <x14:borderColor rgb="FFFFB628"/>
-              <x14:negativeFillColor rgb="FFFF0000"/>
-              <x14:negativeBorderColor rgb="FFFF0000"/>
-              <x14:axisColor rgb="FF000000"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>G6</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C79A09-E0C9-410A-AAF0-F28301E039F1}">
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13439,20 +14765,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
     </row>
     <row r="2" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
       <c r="C2" s="14" t="s">
         <v>1</v>
       </c>
@@ -13463,10 +14789,10 @@
       <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="37"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="15">
         <f>AVERAGE(Data[Amount])</f>
         <v>4136.2299999999996</v>
@@ -13480,10 +14806,10 @@
       <c r="I3" s="21"/>
     </row>
     <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="37"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="15">
         <f>MEDIAN(Data[Amount])</f>
         <v>3437</v>
@@ -13497,10 +14823,10 @@
       <c r="I4" s="21"/>
     </row>
     <row r="5" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="37"/>
+      <c r="B5" s="45"/>
       <c r="C5" s="16">
         <f>MIN(Data[Amount])</f>
         <v>0</v>
@@ -13514,10 +14840,10 @@
       <c r="I5" s="21"/>
     </row>
     <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="37"/>
+      <c r="B6" s="45"/>
       <c r="C6" s="15">
         <f>MAX(Data[Amount])</f>
         <v>16184</v>
@@ -13531,10 +14857,10 @@
       <c r="I6" s="21"/>
     </row>
     <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="37"/>
+      <c r="B7" s="45"/>
       <c r="C7" s="17">
         <f>C6-C5</f>
         <v>16184</v>
@@ -13548,28 +14874,28 @@
       <c r="I7" s="21"/>
     </row>
     <row r="8" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="32"/>
+      <c r="A8" s="36"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="41"/>
       <c r="G8" s="20"/>
       <c r="H8" s="22"/>
       <c r="I8" s="21"/>
     </row>
     <row r="9" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="29"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="34"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
       <c r="G9" s="20"/>
       <c r="H9" s="22"/>
       <c r="I9" s="21"/>
     </row>
     <row r="10" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="44" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="37"/>
+      <c r="B10" s="45"/>
       <c r="C10" s="17">
         <f>_xlfn.PERCENTILE.EXC(Data[Amount],0.25)</f>
         <v>1652</v>
@@ -13583,10 +14909,10 @@
       <c r="I10" s="21"/>
     </row>
     <row r="11" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="37"/>
+      <c r="B11" s="45"/>
       <c r="C11" s="17">
         <f>_xlfn.PERCENTILE.EXC(Data[Amount],0.75)</f>
         <v>6245.75</v>
@@ -13600,10 +14926,10 @@
       <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="36"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="47"/>
       <c r="G12" s="20"/>
       <c r="H12" s="22"/>
       <c r="I12" s="21"/>
@@ -13657,4 +14983,256 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AF3064C-ED3A-4E4B-B9F4-638CA794F10E}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="51">
+        <v>45752</v>
+      </c>
+      <c r="C4" s="50">
+        <v>45752</v>
+      </c>
+      <c r="D4" s="50">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="51">
+        <v>25655</v>
+      </c>
+      <c r="C5" s="50">
+        <v>25655</v>
+      </c>
+      <c r="D5" s="50">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="51">
+        <v>23709</v>
+      </c>
+      <c r="C6" s="50">
+        <v>23709</v>
+      </c>
+      <c r="D6" s="50">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="51">
+        <v>18928</v>
+      </c>
+      <c r="C7" s="50">
+        <v>18928</v>
+      </c>
+      <c r="D7" s="50">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="51">
+        <v>7763</v>
+      </c>
+      <c r="C8" s="50">
+        <v>7763</v>
+      </c>
+      <c r="D8" s="50">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="51">
+        <v>2142</v>
+      </c>
+      <c r="C9" s="50">
+        <v>2142</v>
+      </c>
+      <c r="D9" s="50">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <conditionalFormatting pivot="1" sqref="C4:C9">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="0">
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{88EB78D8-2726-4AF7-9CCD-4D8C8344599C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" pivot="1">
+          <x14:cfRule type="dataBar" id="{88EB78D8-2726-4AF7-9CCD-4D8C8344599C}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF008AEF"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C4:C9</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F18355-1EA3-4A54-BF8B-70117A7E5444}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="52">
+        <v>33.88697318007663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="52">
+        <v>32.301656920077974</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="52">
+        <v>32.807189542483663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="52">
+        <v>37.303128371089535</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="52">
+        <v>44.990867579908674</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="52">
+        <v>35.949565217391303</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>